--- a/Fabric Ontology - extended2/schedule.xlsx
+++ b/Fabric Ontology - extended2/schedule.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Microsoft-Fabric-Graph-sample-set\Fabric Ontology - extended2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9A260B7-BD8F-41FF-930C-3141E998CF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27701E8A-F9A0-44FA-9CC6-9B4642CFD221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BEC26E07-3928-42E2-B052-730D6ABB9FFA}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>line 1</t>
   </si>
@@ -93,6 +91,9 @@
   </si>
   <si>
     <t>FR</t>
+  </si>
+  <si>
+    <t>in total</t>
   </si>
 </sst>
 </file>
@@ -491,13 +492,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0311167-426A-41A9-A463-F39D8AAC3871}">
-  <dimension ref="B2:G17"/>
+  <dimension ref="B2:I17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="9" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>14</v>
       </c>
@@ -514,7 +515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -524,7 +525,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -534,7 +535,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>5</v>
       </c>
@@ -544,7 +545,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -554,7 +555,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>7</v>
       </c>
@@ -564,7 +565,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -574,7 +575,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>9</v>
       </c>
@@ -584,7 +585,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>10</v>
       </c>
@@ -594,7 +595,7 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>11</v>
       </c>
@@ -604,7 +605,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -614,7 +615,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -624,7 +625,12 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>0</v>
       </c>
@@ -643,8 +649,11 @@
       <c r="G15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
@@ -663,8 +672,11 @@
       <c r="G16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>2</v>
       </c>
@@ -682,6 +694,9 @@
       </c>
       <c r="G17">
         <v>2</v>
+      </c>
+      <c r="I17">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
